--- a/Plantilla_Diagnostico_Social_IN_Piura_V4.xlsx
+++ b/Plantilla_Diagnostico_Social_IN_Piura_V4.xlsx
@@ -10432,8 +10432,10 @@
       <c r="Q2" t="s">
         <v>254</v>
       </c>
-      <c r="R2" t="s">
-        <v>245</v>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solo inicial</t>
+        </is>
       </c>
       <c r="S2" t="s">
         <v>283</v>
@@ -10536,8 +10538,10 @@
       <c r="Q3" t="s">
         <v>255</v>
       </c>
-      <c r="R3" t="s">
-        <v>246</v>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inicial + Primaria</t>
+        </is>
       </c>
       <c r="S3" t="s">
         <v>285</v>
@@ -10637,8 +10641,10 @@
       <c r="Q4" t="s">
         <v>256</v>
       </c>
-      <c r="R4" t="s">
-        <v>247</v>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primaria</t>
+        </is>
       </c>
       <c r="S4" t="s">
         <v>287</v>
@@ -10726,8 +10732,10 @@
       <c r="Q5" t="s">
         <v>257</v>
       </c>
-      <c r="R5" t="s">
-        <v>248</v>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Primaria + Secundaria</t>
+        </is>
       </c>
       <c r="S5" t="s">
         <v>289</v>
@@ -10812,8 +10820,10 @@
       <c r="Q6" t="s">
         <v>258</v>
       </c>
-      <c r="R6" t="s">
-        <v>249</v>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inicial + Primaria + Secundaria</t>
+        </is>
       </c>
       <c r="S6" t="s">
         <v>291</v>
@@ -10895,8 +10905,10 @@
       <c r="Q7" t="s">
         <v>259</v>
       </c>
-      <c r="R7" t="s">
-        <v>250</v>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Secundaria</t>
+        </is>
       </c>
       <c r="S7" t="s">
         <v>293</v>
@@ -10948,8 +10960,10 @@
       <c r="Q8" t="s">
         <v>260</v>
       </c>
-      <c r="R8" t="s">
-        <v>251</v>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Superior</t>
+        </is>
       </c>
       <c r="S8" t="s">
         <v>295</v>
@@ -10982,6 +10996,11 @@
       </c>
       <c r="Q9" t="s">
         <v>261</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No hay IE</t>
+        </is>
       </c>
       <c r="S9" t="s">
         <v>297</v>
@@ -12849,12 +12868,16 @@
       <c r="C88" s="118"/>
       <c r="D88" s="118"/>
       <c r="E88" s="118"/>
-      <c r="F88" s="198"/>
-      <c r="G88" s="191"/>
-      <c r="H88" s="191"/>
-      <c r="I88" s="191"/>
-      <c r="J88" s="191"/>
-      <c r="K88" s="191"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inicial + Primaria + Secundaria</t>
+        </is>
+      </c>
+      <c r="H88" s="118"/>
+      <c r="I88" s="118"/>
+      <c r="J88" s="118"/>
+      <c r="K88" s="198"/>
       <c r="L88" s="191"/>
       <c r="M88" s="191"/>
       <c r="N88" s="199"/>
@@ -13845,7 +13868,7 @@
       <c r="N140" s="126"/>
     </row>
   </sheetData>
-  <mergeCells count="289">
+  <mergeCells count="290">
     <mergeCell ref="L26:N26"/>
     <mergeCell ref="F105:H105"/>
     <mergeCell ref="F106:H106"/>
@@ -14093,7 +14116,8 @@
     <mergeCell ref="B67:G67"/>
     <mergeCell ref="H84:I84"/>
     <mergeCell ref="J84:K84"/>
-    <mergeCell ref="F88:N88"/>
+    <mergeCell ref="G88:J88"/>
+    <mergeCell ref="K88:N88"/>
     <mergeCell ref="L93:M93"/>
     <mergeCell ref="B112:E112"/>
     <mergeCell ref="L87:N87"/>

--- a/Plantilla_Diagnostico_Social_IN_Piura_V4.xlsx
+++ b/Plantilla_Diagnostico_Social_IN_Piura_V4.xlsx
@@ -11311,17 +11311,17 @@
       </c>
       <c r="B9" s="115"/>
       <c r="C9" s="116"/>
-      <c r="D9" s="196"/>
+      <c r="D9" s="263" t="str">
+        <f>IFERROR(VLOOKUP($D$8,_Datos!$A$2:$H$128,3,FALSE()),"")</f>
+        <v/>
+      </c>
       <c r="E9" s="188"/>
       <c r="F9" s="189"/>
       <c r="G9" s="217" t="s">
         <v>120</v>
       </c>
       <c r="H9" s="116"/>
-      <c r="I9" s="263" t="str">
-        <f>IFERROR(VLOOKUP($D$8,_Datos!$A$2:$H$128,3,FALSE()),"")</f>
-        <v/>
-      </c>
+      <c r="I9" s="196"/>
       <c r="J9" s="115"/>
       <c r="K9" s="116"/>
       <c r="L9" s="8" t="s">

--- a/Plantilla_Diagnostico_Social_IN_Piura_V4.xlsx
+++ b/Plantilla_Diagnostico_Social_IN_Piura_V4.xlsx
@@ -17808,8 +17808,10 @@
     </row>
     <row r="25" spans="1:14" s="48" customFormat="1" ht="30.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A25" s="65"/>
-      <c r="B25" s="321" t="s">
-        <v>393</v>
+      <c r="B25" s="321" t="inlineStr">
+        <is>
+          <t>Papelógrafos</t>
+        </is>
       </c>
       <c r="C25" s="118"/>
       <c r="D25" s="118"/>
@@ -20524,13 +20526,13 @@
           <x14:formula1>
             <xm:f>_Listas!$Y$2:$Y$6</xm:f>
           </x14:formula1>
-          <xm:sqref>D14 D15 D16 D17 D18 D19 D20 D21</xm:sqref>
+          <xm:sqref>F14 F15 F16 F17 F18 F19 F20 F21</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0500-000002000000}">
           <x14:formula1>
             <xm:f>_Listas!$Z$2:$Z$7</xm:f>
           </x14:formula1>
-          <xm:sqref>E14 E15 E16 E17 E18 E19 E20 E21</xm:sqref>
+          <xm:sqref>G14 G15 G16 G17 G18 G19 G20 G21</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
